--- a/declaration_forms/016_language_preference_declaration_form--declaration_forms.xlsx
+++ b/declaration_forms/016_language_preference_declaration_form--declaration_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,12 +437,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E17"/>
+  <dimension ref="A1:E16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
     <col width="28" customWidth="1" min="2" max="2"/>
-    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -520,12 +520,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>language_preference</t>
+          <t>preferred_language</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>language_preference</t>
+          <t>What is your preferred language?</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -548,7 +548,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>primary_language</t>
+          <t>What is your primary language?</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -571,7 +571,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>contact_language</t>
+          <t>What is your preferred contact language?</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -594,7 +594,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>translation_needs</t>
+          <t>How much translation needs do you have?</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -617,7 +617,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>main_english_language</t>
+          <t>Do you have a primary English language proficiency?</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -640,7 +640,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>language_of_documents</t>
+          <t>What language are documents usually in for your work?</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -663,7 +663,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>preferred_contact_language</t>
+          <t>Preferred Contact Language</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -681,12 +681,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>primary_language</t>
+          <t>primary_language_2</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>primary_language</t>
+          <t>Primary Language 2</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -699,17 +699,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>contact_language</t>
+          <t>main_english_language_2</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>contact_language</t>
+          <t>Do you have a main English language proficiency?</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -727,12 +727,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>translation_needs</t>
+          <t>language_needs</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>translation_needs</t>
+          <t>What translation needs do you have in your work?</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -745,17 +745,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>main_english_language</t>
+          <t>document_language</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>main_english_language</t>
+          <t>Document Language</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -773,12 +773,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>language_of_documents</t>
+          <t>preferred_language_2</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>language_of_documents</t>
+          <t>Preferred Language 2</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -796,39 +796,16 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>preferred_contact_language</t>
+          <t>primary_language_3</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>preferred_contact_language</t>
+          <t>Primary Language 3</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>primary_language</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>primary_language</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -845,12 +822,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C51"/>
+  <dimension ref="A1:C42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
-    <col width="31" customWidth="1" min="2" max="2"/>
-    <col width="31" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -873,51 +850,51 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>language_preference_choices</t>
+          <t>preferred_language_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'english'}</t>
+          <t>english</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'English'}</t>
+          <t>English</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>language_preference_choices</t>
+          <t>preferred_language_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'spanish'}</t>
+          <t>spanish</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Spanish'}</t>
+          <t>Spanish</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>language_preference_choices</t>
+          <t>preferred_language_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'french'}</t>
+          <t>french</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'French'}</t>
+          <t>French</t>
         </is>
       </c>
     </row>
@@ -929,12 +906,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'english'}</t>
+          <t>english</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'English'}</t>
+          <t>English</t>
         </is>
       </c>
     </row>
@@ -946,12 +923,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'spanish'}</t>
+          <t>spanish</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Spanish'}</t>
+          <t>Spanish</t>
         </is>
       </c>
     </row>
@@ -963,12 +940,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'french'}</t>
+          <t>french</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'French'}</t>
+          <t>French</t>
         </is>
       </c>
     </row>
@@ -980,12 +957,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'english'}</t>
+          <t>english</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'English'}</t>
+          <t>English</t>
         </is>
       </c>
     </row>
@@ -997,12 +974,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'spanish'}</t>
+          <t>spanish</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Spanish'}</t>
+          <t>Spanish</t>
         </is>
       </c>
     </row>
@@ -1014,12 +991,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'french'}</t>
+          <t>french</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'French'}</t>
+          <t>French</t>
         </is>
       </c>
     </row>
@@ -1031,12 +1008,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'none'}</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'None'}</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -1048,12 +1025,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'english'}</t>
+          <t>english</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'English'}</t>
+          <t>English</t>
         </is>
       </c>
     </row>
@@ -1065,12 +1042,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'spanish'}</t>
+          <t>spanish</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Spanish'}</t>
+          <t>Spanish</t>
         </is>
       </c>
     </row>
@@ -1082,29 +1059,29 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'french'}</t>
+          <t>french</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'French'}</t>
+          <t>French</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>translation_needs_choices</t>
+          <t>main_english_language_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_5,_'name':_'arabic'}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 5, 'name': 'Arabic'}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1116,12 +1093,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_true}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': True}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1133,29 +1110,29 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_false}</t>
+          <t>not_sure</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': False}</t>
+          <t>Not sure</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>main_english_language_choices</t>
+          <t>language_of_documents_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'not_sure'}</t>
+          <t>english</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Not sure'}</t>
+          <t>English</t>
         </is>
       </c>
     </row>
@@ -1167,12 +1144,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'english'}</t>
+          <t>spanish</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'English'}</t>
+          <t>Spanish</t>
         </is>
       </c>
     </row>
@@ -1184,46 +1161,46 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'spanish'}</t>
+          <t>french</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Spanish'}</t>
+          <t>French</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>language_of_documents_choices</t>
+          <t>preferred_contact_language_choices</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'french'}</t>
+          <t>english</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'French'}</t>
+          <t>English</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>language_of_documents_choices</t>
+          <t>preferred_contact_language_choices</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'arabic'}</t>
+          <t>spanish</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'Arabic'}</t>
+          <t>Spanish</t>
         </is>
       </c>
     </row>
@@ -1235,488 +1212,335 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'english'}</t>
+          <t>french</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'English'}</t>
+          <t>French</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>preferred_contact_language_choices</t>
+          <t>primary_language_2_choices</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'spanish'}</t>
+          <t>english</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Spanish'}</t>
+          <t>English</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>preferred_contact_language_choices</t>
+          <t>primary_language_2_choices</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'french'}</t>
+          <t>spanish</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'French'}</t>
+          <t>Spanish</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>preferred_contact_language_choices</t>
+          <t>primary_language_2_choices</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'arabic'}</t>
+          <t>french</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'Arabic'}</t>
+          <t>French</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>primary_language_choices</t>
+          <t>main_english_language_2_choices</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'english'}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'English'}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>primary_language_choices</t>
+          <t>main_english_language_2_choices</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'spanish'}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Spanish'}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>primary_language_choices</t>
+          <t>main_english_language_2_choices</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'french'}</t>
+          <t>not_sure</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'French'}</t>
+          <t>Not sure</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>contact_language_choices</t>
+          <t>language_needs_choices</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'english'}</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'English'}</t>
+          <t>None</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>contact_language_choices</t>
+          <t>language_needs_choices</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'spanish'}</t>
+          <t>english</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Spanish'}</t>
+          <t>English</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>contact_language_choices</t>
+          <t>language_needs_choices</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'french'}</t>
+          <t>spanish</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'French'}</t>
+          <t>Spanish</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>translation_needs_choices</t>
+          <t>language_needs_choices</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'none'}</t>
+          <t>french</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'None'}</t>
+          <t>French</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>translation_needs_choices</t>
+          <t>document_language_choices</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'english'}</t>
+          <t>english</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'English'}</t>
+          <t>English</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>translation_needs_choices</t>
+          <t>document_language_choices</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'spanish'}</t>
+          <t>spanish</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Spanish'}</t>
+          <t>Spanish</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>translation_needs_choices</t>
+          <t>document_language_choices</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'french'}</t>
+          <t>french</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'French'}</t>
+          <t>French</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>translation_needs_choices</t>
+          <t>preferred_language_2_choices</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>{'id':_5,_'name':_'arabic'}</t>
+          <t>english</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>{'id': 5, 'name': 'Arabic'}</t>
+          <t>English</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>main_english_language_choices</t>
+          <t>preferred_language_2_choices</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_true}</t>
+          <t>spanish</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': True}</t>
+          <t>Spanish</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>main_english_language_choices</t>
+          <t>preferred_language_2_choices</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_false}</t>
+          <t>french</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': False}</t>
+          <t>French</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>main_english_language_choices</t>
+          <t>primary_language_3_choices</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'not_sure'}</t>
+          <t>english</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Not sure'}</t>
+          <t>English</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>language_of_documents_choices</t>
+          <t>primary_language_3_choices</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'english'}</t>
+          <t>spanish</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'English'}</t>
+          <t>Spanish</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>language_of_documents_choices</t>
+          <t>primary_language_3_choices</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'spanish'}</t>
+          <t>french</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Spanish'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>language_of_documents_choices</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>{'id':_3,_'name':_'french'}</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>{'id': 3, 'name': 'French'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>language_of_documents_choices</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>{'id':_4,_'name':_'arabic'}</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>{'id': 4, 'name': 'Arabic'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>preferred_contact_language_choices</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>{'id':_1,_'name':_'english'}</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>{'id': 1, 'name': 'English'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>preferred_contact_language_choices</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>{'id':_2,_'name':_'spanish'}</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>{'id': 2, 'name': 'Spanish'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>preferred_contact_language_choices</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>{'id':_3,_'name':_'french'}</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>{'id': 3, 'name': 'French'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>preferred_contact_language_choices</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>{'id':_4,_'name':_'arabic'}</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>{'id': 4, 'name': 'Arabic'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>primary_language_choices</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>{'id':_1,_'name':_'english'}</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>{'id': 1, 'name': 'English'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>primary_language_choices</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>{'id':_2,_'name':_'spanish'}</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>{'id': 2, 'name': 'Spanish'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>primary_language_choices</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>{'id':_3,_'name':_'french'}</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>{'id': 3, 'name': 'French'}</t>
+          <t>French</t>
         </is>
       </c>
     </row>
